--- a/redmine-logger/backend/user_data/lumiqshubh23/input.xlsx
+++ b/redmine-logger/backend/user_data/lumiqshubh23/input.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F248"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2279,9 +2279,3089 @@
         <v>9a8e40da79daed6e65fd0e6ae77f596a4852e663</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="B95">
+        <v>158484</v>
+      </c>
+      <c r="C95">
+        <v>2</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E95" t="str">
+        <v>DM-22984 deathcover factor in igf</v>
+      </c>
+      <c r="F95" t="str">
+        <v>5033a821c6e25b95378953140ed14edca12d0e84</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="B96">
+        <v>158484</v>
+      </c>
+      <c r="C96">
+        <v>2</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E96" t="str">
+        <v>DM-23043</v>
+      </c>
+      <c r="F96" t="str">
+        <v>7772684e682945f39c9cd52d75cb5bdb0c27e994</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="B97">
+        <v>158484</v>
+      </c>
+      <c r="C97">
+        <v>2</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E97" t="str">
+        <v>secureInvest  continue button issue</v>
+      </c>
+      <c r="F97" t="str">
+        <v>d1b7e2f9d0fc330e4ec7fbf4b0baf95ef0b0f544</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="B98">
+        <v>158484</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E98" t="str">
+        <v>DM-22984 deathcover factor in igf</v>
+      </c>
+      <c r="F98" t="str">
+        <v>4da85214ae597eb1e2f8374528e43ce57fb426da</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B99">
+        <v>158484</v>
+      </c>
+      <c r="C99">
+        <v>1.14</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E99" t="str">
+        <v>DM-23087 The “Are you opting for Staff Discount?” option should be placed after the “Annual Income” field.</v>
+      </c>
+      <c r="F99" t="str">
+        <v>09c6c080804f72a8df6c44653f478851330fccd8</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B100">
+        <v>158484</v>
+      </c>
+      <c r="C100">
+        <v>1.14</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E100" t="str">
+        <v>DM-23089 "Are you opting for Staff Discount?"option is currently displayed in the Life Assured (LA) Details section</v>
+      </c>
+      <c r="F100" t="str">
+        <v>15bd27fe6965ad8aa560d25a8a9f8c20cb5f1dd4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B101">
+        <v>158484</v>
+      </c>
+      <c r="C101">
+        <v>1.14</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E101" t="str">
+        <v>DM-22975 || Validation need to be implement for Illiterate Education</v>
+      </c>
+      <c r="F101" t="str">
+        <v>eb7cf33323d4a62471b0bbea27611f71d129673d</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B102">
+        <v>158484</v>
+      </c>
+      <c r="C102">
+        <v>1.14</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E102" t="str">
+        <v>DM-23070 Pincode api run after clicking outside the field</v>
+      </c>
+      <c r="F102" t="str">
+        <v>45239ff3a1193cb91d9b366fda2e615d55aaf5ed</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B103">
+        <v>158484</v>
+      </c>
+      <c r="C103">
+        <v>1.14</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E103" t="str">
+        <v>secure Invest afr fix</v>
+      </c>
+      <c r="F103" t="str">
+        <v>38d50b8f7fac49f9b16d29c8582958bbb40ae9ff</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B104">
+        <v>158484</v>
+      </c>
+      <c r="C104">
+        <v>1.14</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E104" t="str">
+        <v>secure Invest afr fix</v>
+      </c>
+      <c r="F104" t="str">
+        <v>5e4a4a77c57a009e00e9661f54a8f2b620d3e266</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B105">
+        <v>158484</v>
+      </c>
+      <c r="C105">
+        <v>1.16</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E105" t="str">
+        <v>AFR secureInvest fix</v>
+      </c>
+      <c r="F105" t="str">
+        <v>739b615da1d9543e4789cb3344123091ec373359</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="B106">
+        <v>158484</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Revert "alternative number added"</v>
+      </c>
+      <c r="F106" t="str">
+        <v>60606c0a103f76c72422f3155668650136edcd40</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="B107">
+        <v>158484</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E107" t="str">
+        <v>alternative number added</v>
+      </c>
+      <c r="F107" t="str">
+        <v>370237486317451707c49b64a237b56148ad9bc7</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="B108">
+        <v>158484</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E108" t="str">
+        <v>rop error msg fix</v>
+      </c>
+      <c r="F108" t="str">
+        <v>b37bc9ee06f2575abaa1113396367f1ac801bdff</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="B109">
+        <v>158484</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E109" t="str">
+        <v>wealth edge fund issue fix</v>
+      </c>
+      <c r="F109" t="str">
+        <v>a3c9496d6ae1e5d5bed1bff81002ff7360c4d36a</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="B110">
+        <v>158484</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E110" t="str">
+        <v>Revert "alternative number issue fix"</v>
+      </c>
+      <c r="F110" t="str">
+        <v>8dd15cad942ac9c5b1b38cb21d1771c9a1174106</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="B111">
+        <v>158484</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E111" t="str">
+        <v>Revert "alternative number issue fix"</v>
+      </c>
+      <c r="F111" t="str">
+        <v>0a55e9ebf9206acc4b9644f3bb288f73e8b9e9ab</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="B112">
+        <v>158484</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E112" t="str">
+        <v>alternative number issue fix</v>
+      </c>
+      <c r="F112" t="str">
+        <v>4d9ff2bbc2940e10af61c44bbdf114ec1da39cce</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="B113">
+        <v>158484</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E113" t="str">
+        <v>wealth edge fund issue fix</v>
+      </c>
+      <c r="F113" t="str">
+        <v>b056e72bb1427b69544bc2672d0fef06b2d8aa00</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B114">
+        <v>158484</v>
+      </c>
+      <c r="C114">
+        <v>0.8</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E114" t="str">
+        <v>spelling mistake fix</v>
+      </c>
+      <c r="F114" t="str">
+        <v>4a829a71dfd645d746a114dcaeabd3646dfd11f4</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B115">
+        <v>158484</v>
+      </c>
+      <c r="C115">
+        <v>0.8</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E115" t="str">
+        <v>mariner field issue</v>
+      </c>
+      <c r="F115" t="str">
+        <v>6f8e7ceed8731e893cf5fc9d2577123d8cd996f3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B116">
+        <v>158484</v>
+      </c>
+      <c r="C116">
+        <v>0.8</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E116" t="str">
+        <v>wealth edge continue issue fix</v>
+      </c>
+      <c r="F116" t="str">
+        <v>76bc99847e8c16318d11785e10b6e8abc52001c1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B117">
+        <v>158484</v>
+      </c>
+      <c r="C117">
+        <v>0.8</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E117" t="str">
+        <v>bi pdf through sms</v>
+      </c>
+      <c r="F117" t="str">
+        <v>af1fabf41c1901c58a4535fe6c49933536afed1c</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B118">
+        <v>158484</v>
+      </c>
+      <c r="C118">
+        <v>0.8</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E118" t="str">
+        <v>DM-23175</v>
+      </c>
+      <c r="F118" t="str">
+        <v>0dd43a17d6c491ce1212b63b140285018b28922e</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B119">
+        <v>158484</v>
+      </c>
+      <c r="C119">
+        <v>0.8</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E119" t="str">
+        <v>DM-22975 illitrate mapping</v>
+      </c>
+      <c r="F119" t="str">
+        <v>cbaaa9fedfb48e753e7ee7c11737ea9887fb225f</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B120">
+        <v>158484</v>
+      </c>
+      <c r="C120">
+        <v>0.8</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E120" t="str">
+        <v>address flow chnage</v>
+      </c>
+      <c r="F120" t="str">
+        <v>bbca155bf05e640939b18486d9a0e0b20f7cf62e</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B121">
+        <v>158484</v>
+      </c>
+      <c r="C121">
+        <v>0.8</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E121" t="str">
+        <v>annur address fallback</v>
+      </c>
+      <c r="F121" t="str">
+        <v>678fc16bb8739ee547ad73d3f0bd1f5c54e505b9</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B122">
+        <v>158484</v>
+      </c>
+      <c r="C122">
+        <v>0.8</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E122" t="str">
+        <v>bi pdf send by sms</v>
+      </c>
+      <c r="F122" t="str">
+        <v>f7c649e597a497bbe9ff905d9a892829c304b7dd</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B123">
+        <v>158484</v>
+      </c>
+      <c r="C123">
+        <v>0.8</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E123" t="str">
+        <v>address flow change</v>
+      </c>
+      <c r="F123" t="str">
+        <v>21892dc6f20330ce73fb39e694fcf32a02f82fb2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="B124">
+        <v>158484</v>
+      </c>
+      <c r="C124">
+        <v>1.33</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E124" t="str">
+        <v>secure invest sto fund logic</v>
+      </c>
+      <c r="F124" t="str">
+        <v>0f8491441ef27c57ea6a99411132fb25e32eda21</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="B125">
+        <v>158484</v>
+      </c>
+      <c r="C125">
+        <v>1.33</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E125" t="str">
+        <v>Revert "DM-23121 if single option then autoSelect"</v>
+      </c>
+      <c r="F125" t="str">
+        <v>298c2849370ac0d64d6c362b14e9ebdb63501646</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="B126">
+        <v>158484</v>
+      </c>
+      <c r="C126">
+        <v>1.33</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E126" t="str">
+        <v>aadhar masked when 12 diigit</v>
+      </c>
+      <c r="F126" t="str">
+        <v>42e680234bb7454719e3e454aa541d9cda441ab4</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="B127">
+        <v>158484</v>
+      </c>
+      <c r="C127">
+        <v>1.33</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E127" t="str">
+        <v>DM-23121 if single option then autoSelect</v>
+      </c>
+      <c r="F127" t="str">
+        <v>093f9840d78111faaa0b8ba1bc26b576dd7b76ac</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="B128">
+        <v>158484</v>
+      </c>
+      <c r="C128">
+        <v>1.33</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E128" t="str">
+        <v>DM-23121 if single option then autoSelect</v>
+      </c>
+      <c r="F128" t="str">
+        <v>696502680c74817d742c55d8828822a6980de037</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="B129">
+        <v>158484</v>
+      </c>
+      <c r="C129">
+        <v>1.35</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E129" t="str">
+        <v>Revert "Merge branch 'uat-common-backend-1' into insure/develop"</v>
+      </c>
+      <c r="F129" t="str">
+        <v>75654a7b2f75608ca72a4aabd3173ab2bc0b8220</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="B130">
+        <v>158484</v>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Meeting</v>
+      </c>
+      <c r="E130" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+      <c r="F130" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="B131">
+        <v>158484</v>
+      </c>
+      <c r="C131">
+        <v>4</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E131" t="str">
+        <v>address issue fix</v>
+      </c>
+      <c r="F131" t="str">
+        <v>7637c5f2c4be9ed9ed8935f70d6dc7b30440f6b8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="B132">
+        <v>158484</v>
+      </c>
+      <c r="C132">
+        <v>4</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E132" t="str">
+        <v>unified launch fix</v>
+      </c>
+      <c r="F132" t="str">
+        <v>91050bad32cff7f947f03d8dbb655eefeb526da6</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="B133">
+        <v>158484</v>
+      </c>
+      <c r="C133">
+        <v>2.67</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E133" t="str">
+        <v>secure invest not fund auto select</v>
+      </c>
+      <c r="F133" t="str">
+        <v>39fd1833bc250a89717977e1e3283d43130b3287</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="B134">
+        <v>158484</v>
+      </c>
+      <c r="C134">
+        <v>2.67</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E134" t="str">
+        <v>annur wealth edge issue fix</v>
+      </c>
+      <c r="F134" t="str">
+        <v>50f6c88d2c7fbab5c57efaa5723a34b71f4386a0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="B135">
+        <v>158484</v>
+      </c>
+      <c r="C135">
+        <v>2.66</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E135" t="str">
+        <v>annur wealth edge issue fix</v>
+      </c>
+      <c r="F135" t="str">
+        <v>fb98a858a1d9171ad1034e58e522088a2de06040</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="B136">
+        <v>158484</v>
+      </c>
+      <c r="C136">
+        <v>2</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E136" t="str">
+        <v>secureInvest liquide fund issue fix</v>
+      </c>
+      <c r="F136" t="str">
+        <v>db04074e51693acf46994b47b89ae6221301b597</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="B137">
+        <v>158484</v>
+      </c>
+      <c r="C137">
+        <v>2</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E137" t="str">
+        <v>secureInvest whole life option</v>
+      </c>
+      <c r="F137" t="str">
+        <v>01fb61970864ac23e69baf11116af08bba99c552</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="B138">
+        <v>158484</v>
+      </c>
+      <c r="C138">
+        <v>2</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E138" t="str">
+        <v>polically exposed</v>
+      </c>
+      <c r="F138" t="str">
+        <v>50142c32072b7d8e388fd84c1502d1769de90711</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="B139">
+        <v>158484</v>
+      </c>
+      <c r="C139">
+        <v>2</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E139" t="str">
+        <v>secureInvest liquid fund issue fix</v>
+      </c>
+      <c r="F139" t="str">
+        <v>ce45ff0a3a2bcea5d9f55790894c0dbf9ab9a78c</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="B140">
+        <v>158484</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E140" t="str">
+        <v>If PO/LA is NRI but not mariner, current address outside India mandatory</v>
+      </c>
+      <c r="F140" t="str">
+        <v>4f07e17fae2fa8cb32e3bf179b06b7e20fe8942f</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="B141">
+        <v>158484</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+      <c r="D141" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E141" t="str">
+        <v>pan number must be 10</v>
+      </c>
+      <c r="F141" t="str">
+        <v>6cf0060bb8f1341fd076662f36f21ea3ff1bf2e5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="B142">
+        <v>158484</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+      <c r="D142" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E142" t="str">
+        <v>Relationship with PEP other field add</v>
+      </c>
+      <c r="F142" t="str">
+        <v>37de77bf0a1c9579237aa77cced98d5f64dfd18c</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="B143">
+        <v>158484</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E143" t="str">
+        <v>Employment questions for proposer should apply to LA; exclude if LA housewife</v>
+      </c>
+      <c r="F143" t="str">
+        <v>54688bbceecfe9edf3baff9717ace090b07f228f</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="B144">
+        <v>158484</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
+      </c>
+      <c r="D144" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E144" t="str">
+        <v>PO personal Health details should not come for form 2 cases</v>
+      </c>
+      <c r="F144" t="str">
+        <v>d9b9549bf78158a844a9ce66cea71510c9ba251b</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="B145">
+        <v>158484</v>
+      </c>
+      <c r="C145">
+        <v>1</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E145" t="str">
+        <v>for 2 case questionior handle</v>
+      </c>
+      <c r="F145" t="str">
+        <v>09fd7f027227956b052b1b960c1097944cb1a60f</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="B146">
+        <v>158484</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E146" t="str">
+        <v>If PO is Mariner, industry defaults to Merchant Marine (frozen)</v>
+      </c>
+      <c r="F146" t="str">
+        <v>cb4c27537d4c9ac33488c2d2d3ced67deb1ff4d8</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="B147">
+        <v>158484</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E147" t="str">
+        <v>Relationship with PEP other add</v>
+      </c>
+      <c r="F147" t="str">
+        <v>4a4fd0af471fc6cda0950dba62dfb91d2f5d4660</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B148">
+        <v>158484</v>
+      </c>
+      <c r="C148">
+        <v>0.89</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E148" t="str">
+        <v>DM-2394</v>
+      </c>
+      <c r="F148" t="str">
+        <v>a5ee1019cdcb541ec627f383ab6c9104045f048c</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B149">
+        <v>158484</v>
+      </c>
+      <c r="C149">
+        <v>0.89</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E149" t="str">
+        <v>upload checkbox feature</v>
+      </c>
+      <c r="F149" t="str">
+        <v>b502a004028755e9856792303ca1f5e33726b8a2</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B150">
+        <v>158484</v>
+      </c>
+      <c r="C150">
+        <v>0.89</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E150" t="str">
+        <v>Revert "address proof type also added"</v>
+      </c>
+      <c r="F150" t="str">
+        <v>7ba1767399890d1c2cde14e5b2a6a743e86392ff</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B151">
+        <v>158484</v>
+      </c>
+      <c r="C151">
+        <v>0.89</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E151" t="str">
+        <v>address proof type also added</v>
+      </c>
+      <c r="F151" t="str">
+        <v>62940a6c9d80db350938204b6164a4210a6329ca</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B152">
+        <v>158484</v>
+      </c>
+      <c r="C152">
+        <v>0.89</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E152" t="str">
+        <v>annur api fail navigateion</v>
+      </c>
+      <c r="F152" t="str">
+        <v>ca7fe937e633709130fcf2b62edc7582dd30f9f6</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B153">
+        <v>158484</v>
+      </c>
+      <c r="C153">
+        <v>0.89</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E153" t="str">
+        <v>add age proof as per DM-23374</v>
+      </c>
+      <c r="F153" t="str">
+        <v>56f5281030fca42a747e2a596def58064e93f69e</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B154">
+        <v>158484</v>
+      </c>
+      <c r="C154">
+        <v>0.89</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E154" t="str">
+        <v>Revert "address proff type also added"</v>
+      </c>
+      <c r="F154" t="str">
+        <v>ff7e09dae9e6ac17225ec0da9a3734621b2ec3b9</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B155">
+        <v>158484</v>
+      </c>
+      <c r="C155">
+        <v>0.89</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E155" t="str">
+        <v>Revert "address proff type also added"</v>
+      </c>
+      <c r="F155" t="str">
+        <v>719d86992602a3df2a1f779bfd31c67b6e62ef45</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B156">
+        <v>158484</v>
+      </c>
+      <c r="C156">
+        <v>0.88</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E156" t="str">
+        <v>address proff type also added</v>
+      </c>
+      <c r="F156" t="str">
+        <v>85c5e918bb5e2b78022008315fd0d5fe21b6d545</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>2026-06-18</v>
+      </c>
+      <c r="B157">
+        <v>158484</v>
+      </c>
+      <c r="C157">
+        <v>2.67</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E157" t="str">
+        <v>address checkbox fix</v>
+      </c>
+      <c r="F157" t="str">
+        <v>407858e401bc2975e70bdf5856f6ab9b140f0960</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>2026-06-18</v>
+      </c>
+      <c r="B158">
+        <v>158484</v>
+      </c>
+      <c r="C158">
+        <v>2.67</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E158" t="str">
+        <v>add address proof type</v>
+      </c>
+      <c r="F158" t="str">
+        <v>bdb0ea1853713cfe111eda9c06d8564bea6c2b79</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>2026-06-18</v>
+      </c>
+      <c r="B159">
+        <v>158484</v>
+      </c>
+      <c r="C159">
+        <v>2.66</v>
+      </c>
+      <c r="D159" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E159" t="str">
+        <v>address type mapping</v>
+      </c>
+      <c r="F159" t="str">
+        <v>b405ff6497eaf2fb030c2fed60e43d391b9a8e80</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B160">
+        <v>158484</v>
+      </c>
+      <c r="C160">
+        <v>1.33</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E160" t="str">
+        <v>single option auto select</v>
+      </c>
+      <c r="F160" t="str">
+        <v>ec9dd5a17c8e072c718bc67e8f05ba8b58e90c53</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B161">
+        <v>158484</v>
+      </c>
+      <c r="C161">
+        <v>1.33</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E161" t="str">
+        <v>dob check uncheck issue fix</v>
+      </c>
+      <c r="F161" t="str">
+        <v>d168932caf15589c1b9a12a597b27d05a0826231</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B162">
+        <v>158484</v>
+      </c>
+      <c r="C162">
+        <v>1.33</v>
+      </c>
+      <c r="D162" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E162" t="str">
+        <v>age proof and address proof fix</v>
+      </c>
+      <c r="F162" t="str">
+        <v>08ac7ff4b44fa4830cd3fd240f46d549e398bf83</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B163">
+        <v>158484</v>
+      </c>
+      <c r="C163">
+        <v>1.33</v>
+      </c>
+      <c r="D163" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E163" t="str">
+        <v>address type details</v>
+      </c>
+      <c r="F163" t="str">
+        <v>632f1d16ccc018a57846aed8211535da54451d74</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B164">
+        <v>158484</v>
+      </c>
+      <c r="C164">
+        <v>1.33</v>
+      </c>
+      <c r="D164" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E164" t="str">
+        <v>age proof and address proof fix</v>
+      </c>
+      <c r="F164" t="str">
+        <v>b11d955f30d2894156ee9eb98245716aee19704f</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B165">
+        <v>158484</v>
+      </c>
+      <c r="C165">
+        <v>1.35</v>
+      </c>
+      <c r="D165" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E165" t="str">
+        <v>address type details</v>
+      </c>
+      <c r="F165" t="str">
+        <v>3a837721569e94449274103a7ec882e69bc4e14d</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>2026-06-23</v>
+      </c>
+      <c r="B166">
+        <v>158484</v>
+      </c>
+      <c r="C166">
+        <v>2</v>
+      </c>
+      <c r="D166" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E166" t="str">
+        <v>heading driver question</v>
+      </c>
+      <c r="F166" t="str">
+        <v>6fb9c4b7629345c302e7ec197ca778d0ef9846cc</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>2026-06-23</v>
+      </c>
+      <c r="B167">
+        <v>158484</v>
+      </c>
+      <c r="C167">
+        <v>2</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E167" t="str">
+        <v>driver questionar</v>
+      </c>
+      <c r="F167" t="str">
+        <v>2d63fc872425b4c874f97a3dfb2dbafe543b892d</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>2026-06-23</v>
+      </c>
+      <c r="B168">
+        <v>158484</v>
+      </c>
+      <c r="C168">
+        <v>2</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E168" t="str">
+        <v>DM-23546</v>
+      </c>
+      <c r="F168" t="str">
+        <v>e2fca5aca7bbd4758ad5ff5bb7331aa403f5c405</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>2026-06-23</v>
+      </c>
+      <c r="B169">
+        <v>158484</v>
+      </c>
+      <c r="C169">
+        <v>2</v>
+      </c>
+      <c r="D169" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E169" t="str">
+        <v>driver questioner</v>
+      </c>
+      <c r="F169" t="str">
+        <v>6cf47321a603e9d5f4e71d9b3b245c3744a9e8b9</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>2026-06-26</v>
+      </c>
+      <c r="B170">
+        <v>158484</v>
+      </c>
+      <c r="C170">
+        <v>1.6</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E170" t="str">
+        <v>ulip rider plan code</v>
+      </c>
+      <c r="F170" t="str">
+        <v>84f93450837775e7e63ee19b1ab48edbb7039310</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>2026-06-26</v>
+      </c>
+      <c r="B171">
+        <v>158484</v>
+      </c>
+      <c r="C171">
+        <v>1.6</v>
+      </c>
+      <c r="D171" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E171" t="str">
+        <v>dont show harcoded error message on annur</v>
+      </c>
+      <c r="F171" t="str">
+        <v>e22e159cd06c15111919b9408eb0d1435b301574</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>2026-06-26</v>
+      </c>
+      <c r="B172">
+        <v>158484</v>
+      </c>
+      <c r="C172">
+        <v>1.6</v>
+      </c>
+      <c r="D172" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E172" t="str">
+        <v>when no rider directly continue</v>
+      </c>
+      <c r="F172" t="str">
+        <v>c250ba72d7414c93b52250f1a5bbc227aae3d2a0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>2026-06-26</v>
+      </c>
+      <c r="B173">
+        <v>158484</v>
+      </c>
+      <c r="C173">
+        <v>1.6</v>
+      </c>
+      <c r="D173" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E173" t="str">
+        <v>rider plan code for ulip</v>
+      </c>
+      <c r="F173" t="str">
+        <v>50643aac33cb3566db6c57c19a81eec756aa7af0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>2026-06-26</v>
+      </c>
+      <c r="B174">
+        <v>158484</v>
+      </c>
+      <c r="C174">
+        <v>1.6</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E174" t="str">
+        <v>SPF PDF Product name is Missing</v>
+      </c>
+      <c r="F174" t="str">
+        <v>afd2e3d7ee62e112e81ff865b9269a8ab1bbf3d4</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="B175">
+        <v>158484</v>
+      </c>
+      <c r="C175">
+        <v>1</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Meeting</v>
+      </c>
+      <c r="E175" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+      <c r="F175" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="B176">
+        <v>158484</v>
+      </c>
+      <c r="C176">
+        <v>2.67</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E176" t="str">
+        <v>tpa api integration</v>
+      </c>
+      <c r="F176" t="str">
+        <v>4fdf6e55e458c3a76f5390445d65db36ff5fda3e</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="B177">
+        <v>158484</v>
+      </c>
+      <c r="C177">
+        <v>2.67</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E177" t="str">
+        <v>tpa api  integration</v>
+      </c>
+      <c r="F177" t="str">
+        <v>74d1761fc719b203749a19a33d9d9b9707b0fbd1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="B178">
+        <v>158484</v>
+      </c>
+      <c r="C178">
+        <v>2.66</v>
+      </c>
+      <c r="D178" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E178" t="str">
+        <v>DM-23544</v>
+      </c>
+      <c r="F178" t="str">
+        <v>9420abfa690ba5fa1db8814f3c68083639216de2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B179">
+        <v>158484</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E179" t="str">
+        <v>DM-23087 The “Are you opting for Staff Discount?” option should be placed after the “Annual Income” field.</v>
+      </c>
+      <c r="F179" t="str">
+        <v>09c6c080804f72a8df6c44653f478851330fccd8</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B180">
+        <v>158484</v>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E180" t="str">
+        <v>DM-23089 "Are you opting for Staff Discount?"option is currently displayed in the Life Assured (LA) Details section</v>
+      </c>
+      <c r="F180" t="str">
+        <v>15bd27fe6965ad8aa560d25a8a9f8c20cb5f1dd4</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B181">
+        <v>158484</v>
+      </c>
+      <c r="C181">
+        <v>1</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E181" t="str">
+        <v>DM-22975 || Validation need to be implement for Illiterate Education</v>
+      </c>
+      <c r="F181" t="str">
+        <v>eb7cf33323d4a62471b0bbea27611f71d129673d</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B182">
+        <v>158484</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E182" t="str">
+        <v>DM-23070 Pincode api run after clicking outside the field</v>
+      </c>
+      <c r="F182" t="str">
+        <v>45239ff3a1193cb91d9b366fda2e615d55aaf5ed</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B183">
+        <v>158484</v>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+      <c r="D183" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E183" t="str">
+        <v>secure Invest afr fix</v>
+      </c>
+      <c r="F183" t="str">
+        <v>38d50b8f7fac49f9b16d29c8582958bbb40ae9ff</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B184">
+        <v>158484</v>
+      </c>
+      <c r="C184">
+        <v>1</v>
+      </c>
+      <c r="D184" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E184" t="str">
+        <v>secure Invest afr fix</v>
+      </c>
+      <c r="F184" t="str">
+        <v>5e4a4a77c57a009e00e9661f54a8f2b620d3e266</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="B185">
+        <v>158484</v>
+      </c>
+      <c r="C185">
+        <v>2</v>
+      </c>
+      <c r="D185" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E185" t="str">
+        <v>AFR secureInvest fix</v>
+      </c>
+      <c r="F185" t="str">
+        <v>739b615da1d9543e4789cb3344123091ec373359</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B186">
+        <v>158484</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E186" t="str">
+        <v>spelling mistake fix</v>
+      </c>
+      <c r="F186" t="str">
+        <v>4a829a71dfd645d746a114dcaeabd3646dfd11f4</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B187">
+        <v>158484</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E187" t="str">
+        <v>mariner field issue</v>
+      </c>
+      <c r="F187" t="str">
+        <v>6f8e7ceed8731e893cf5fc9d2577123d8cd996f3</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B188">
+        <v>158484</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E188" t="str">
+        <v>wealth edge continue issue fix</v>
+      </c>
+      <c r="F188" t="str">
+        <v>76bc99847e8c16318d11785e10b6e8abc52001c1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B189">
+        <v>158484</v>
+      </c>
+      <c r="C189">
+        <v>1</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E189" t="str">
+        <v>bi pdf through sms</v>
+      </c>
+      <c r="F189" t="str">
+        <v>af1fabf41c1901c58a4535fe6c49933536afed1c</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B190">
+        <v>158484</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E190" t="str">
+        <v>DM-23175</v>
+      </c>
+      <c r="F190" t="str">
+        <v>0dd43a17d6c491ce1212b63b140285018b28922e</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B191">
+        <v>158484</v>
+      </c>
+      <c r="C191">
+        <v>1</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E191" t="str">
+        <v>DM-22975 illitrate mapping</v>
+      </c>
+      <c r="F191" t="str">
+        <v>cbaaa9fedfb48e753e7ee7c11737ea9887fb225f</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B192">
+        <v>158484</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+      <c r="D192" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E192" t="str">
+        <v>address flow chnage</v>
+      </c>
+      <c r="F192" t="str">
+        <v>bbca155bf05e640939b18486d9a0e0b20f7cf62e</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B193">
+        <v>158484</v>
+      </c>
+      <c r="C193">
+        <v>1</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E193" t="str">
+        <v>annur address fallback</v>
+      </c>
+      <c r="F193" t="str">
+        <v>678fc16bb8739ee547ad73d3f0bd1f5c54e505b9</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B194">
+        <v>158484</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E194" t="str">
+        <v>bi pdf send by sms</v>
+      </c>
+      <c r="F194" t="str">
+        <v>f7c649e597a497bbe9ff905d9a892829c304b7dd</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="B195">
+        <v>158484</v>
+      </c>
+      <c r="C195">
+        <v>-1</v>
+      </c>
+      <c r="D195" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E195" t="str">
+        <v>address flow change</v>
+      </c>
+      <c r="F195" t="str">
+        <v>21892dc6f20330ce73fb39e694fcf32a02f82fb2</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="B196">
+        <v>158484</v>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E196" t="str">
+        <v>secure invest sto fund logic</v>
+      </c>
+      <c r="F196" t="str">
+        <v>0f8491441ef27c57ea6a99411132fb25e32eda21</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="B197">
+        <v>158484</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E197" t="str">
+        <v>Revert "DM-23121 if single option then autoSelect"</v>
+      </c>
+      <c r="F197" t="str">
+        <v>298c2849370ac0d64d6c362b14e9ebdb63501646</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="B198">
+        <v>158484</v>
+      </c>
+      <c r="C198">
+        <v>1</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E198" t="str">
+        <v>aadhar masked when 12 diigit</v>
+      </c>
+      <c r="F198" t="str">
+        <v>42e680234bb7454719e3e454aa541d9cda441ab4</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="B199">
+        <v>158484</v>
+      </c>
+      <c r="C199">
+        <v>1</v>
+      </c>
+      <c r="D199" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E199" t="str">
+        <v>DM-23121 if single option then autoSelect</v>
+      </c>
+      <c r="F199" t="str">
+        <v>093f9840d78111faaa0b8ba1bc26b576dd7b76ac</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="B200">
+        <v>158484</v>
+      </c>
+      <c r="C200">
+        <v>1</v>
+      </c>
+      <c r="D200" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E200" t="str">
+        <v>DM-23121 if single option then autoSelect</v>
+      </c>
+      <c r="F200" t="str">
+        <v>696502680c74817d742c55d8828822a6980de037</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="B201">
+        <v>158484</v>
+      </c>
+      <c r="C201">
+        <v>3</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E201" t="str">
+        <v>Revert "Merge branch 'uat-common-backend-1' into insure/develop"</v>
+      </c>
+      <c r="F201" t="str">
+        <v>75654a7b2f75608ca72a4aabd3173ab2bc0b8220</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="B202">
+        <v>158484</v>
+      </c>
+      <c r="C202">
+        <v>2</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E202" t="str">
+        <v>secure invest not fund auto select</v>
+      </c>
+      <c r="F202" t="str">
+        <v>39fd1833bc250a89717977e1e3283d43130b3287</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="B203">
+        <v>158484</v>
+      </c>
+      <c r="C203">
+        <v>2</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E203" t="str">
+        <v>annur wealth edge issue fix</v>
+      </c>
+      <c r="F203" t="str">
+        <v>50f6c88d2c7fbab5c57efaa5723a34b71f4386a0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="B204">
+        <v>158484</v>
+      </c>
+      <c r="C204">
+        <v>4</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E204" t="str">
+        <v>annur wealth edge issue fix</v>
+      </c>
+      <c r="F204" t="str">
+        <v>fb98a858a1d9171ad1034e58e522088a2de06040</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="B205">
+        <v>158484</v>
+      </c>
+      <c r="C205">
+        <v>1</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E205" t="str">
+        <v>uncheck dob feature</v>
+      </c>
+      <c r="F205" t="str">
+        <v>ead293f3b06815288e7967a7bb7e52107e7f6c94</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="B206">
+        <v>158484</v>
+      </c>
+      <c r="C206">
+        <v>1</v>
+      </c>
+      <c r="D206" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E206" t="str">
+        <v>adress flow change by enhancement</v>
+      </c>
+      <c r="F206" t="str">
+        <v>3097285a98b6d6a00da498f480f76072c6e1c592</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="B207">
+        <v>158484</v>
+      </c>
+      <c r="C207">
+        <v>1</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E207" t="str">
+        <v>address enhanacement</v>
+      </c>
+      <c r="F207" t="str">
+        <v>1df15fe16d18561d9ae557d4af7f483a2d1939df</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="B208">
+        <v>158484</v>
+      </c>
+      <c r="C208">
+        <v>1</v>
+      </c>
+      <c r="D208" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E208" t="str">
+        <v>annur navigate to next even if api fail</v>
+      </c>
+      <c r="F208" t="str">
+        <v>c7f0f41075db3410129cceeaf5f971b6c742e667</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="B209">
+        <v>158484</v>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="D209" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E209" t="str">
+        <v>add speical character validation on address</v>
+      </c>
+      <c r="F209" t="str">
+        <v>a385b36d4af4fbaa692a2bb9c9b9d071bdf973d7</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="B210">
+        <v>158484</v>
+      </c>
+      <c r="C210">
+        <v>3</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E210" t="str">
+        <v>wealth edge issue fix</v>
+      </c>
+      <c r="F210" t="str">
+        <v>ac9e7046f9f21089761a6d96c097f94bb0ed7165</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B211">
+        <v>158484</v>
+      </c>
+      <c r="C211">
+        <v>1</v>
+      </c>
+      <c r="D211" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E211" t="str">
+        <v>DM-2394</v>
+      </c>
+      <c r="F211" t="str">
+        <v>a5ee1019cdcb541ec627f383ab6c9104045f048c</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B212">
+        <v>158484</v>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+      <c r="D212" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E212" t="str">
+        <v>upload checkbox feature</v>
+      </c>
+      <c r="F212" t="str">
+        <v>b502a004028755e9856792303ca1f5e33726b8a2</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B213">
+        <v>158484</v>
+      </c>
+      <c r="C213">
+        <v>1</v>
+      </c>
+      <c r="D213" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E213" t="str">
+        <v>Revert "address proof type also added"</v>
+      </c>
+      <c r="F213" t="str">
+        <v>7ba1767399890d1c2cde14e5b2a6a743e86392ff</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B214">
+        <v>158484</v>
+      </c>
+      <c r="C214">
+        <v>1</v>
+      </c>
+      <c r="D214" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E214" t="str">
+        <v>address proof type also added</v>
+      </c>
+      <c r="F214" t="str">
+        <v>62940a6c9d80db350938204b6164a4210a6329ca</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B215">
+        <v>158484</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+      <c r="D215" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E215" t="str">
+        <v>annur api fail navigateion</v>
+      </c>
+      <c r="F215" t="str">
+        <v>ca7fe937e633709130fcf2b62edc7582dd30f9f6</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B216">
+        <v>158484</v>
+      </c>
+      <c r="C216">
+        <v>1</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E216" t="str">
+        <v>add age proof as per DM-23374</v>
+      </c>
+      <c r="F216" t="str">
+        <v>56f5281030fca42a747e2a596def58064e93f69e</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B217">
+        <v>158484</v>
+      </c>
+      <c r="C217">
+        <v>1</v>
+      </c>
+      <c r="D217" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E217" t="str">
+        <v>Revert "address proff type also added"</v>
+      </c>
+      <c r="F217" t="str">
+        <v>ff7e09dae9e6ac17225ec0da9a3734621b2ec3b9</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B218">
+        <v>158484</v>
+      </c>
+      <c r="C218">
+        <v>1</v>
+      </c>
+      <c r="D218" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E218" t="str">
+        <v>Revert "address proff type also added"</v>
+      </c>
+      <c r="F218" t="str">
+        <v>719d86992602a3df2a1f779bfd31c67b6e62ef45</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="B219">
+        <v>158484</v>
+      </c>
+      <c r="C219">
+        <v>1</v>
+      </c>
+      <c r="D219" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E219" t="str">
+        <v>address proff type also added</v>
+      </c>
+      <c r="F219" t="str">
+        <v>85c5e918bb5e2b78022008315fd0d5fe21b6d545</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>2026-06-16</v>
+      </c>
+      <c r="B220">
+        <v>158484</v>
+      </c>
+      <c r="C220">
+        <v>1</v>
+      </c>
+      <c r="D220" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E220" t="str">
+        <v>Dm-23443</v>
+      </c>
+      <c r="F220" t="str">
+        <v>f2fe5fcd220af0cf8bd4bc27899735ade613a321</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>2026-06-16</v>
+      </c>
+      <c r="B221">
+        <v>158484</v>
+      </c>
+      <c r="C221">
+        <v>1</v>
+      </c>
+      <c r="D221" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E221" t="str">
+        <v>DM-23381</v>
+      </c>
+      <c r="F221" t="str">
+        <v>ff9fd4f1691ccfc490c3d03f1c0095e68eefc42b</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>2026-06-16</v>
+      </c>
+      <c r="B222">
+        <v>158484</v>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+      <c r="D222" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E222" t="str">
+        <v>pan validation error msg</v>
+      </c>
+      <c r="F222" t="str">
+        <v>d5a54a5cd7a0774aaf5d181e53979f5098e26522</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>2026-06-16</v>
+      </c>
+      <c r="B223">
+        <v>158484</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E223" t="str">
+        <v>Non - School Going Child have value 185</v>
+      </c>
+      <c r="F223" t="str">
+        <v>25c68f96763134e98d0a9ea38a91c154157a7cfa</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>2026-06-16</v>
+      </c>
+      <c r="B224">
+        <v>158484</v>
+      </c>
+      <c r="C224">
+        <v>4</v>
+      </c>
+      <c r="D224" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E224" t="str">
+        <v>Dm-23443</v>
+      </c>
+      <c r="F224" t="str">
+        <v>3e07715dfd25da43ca278839e96c01e446ef161a</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>2026-06-18</v>
+      </c>
+      <c r="B225">
+        <v>158484</v>
+      </c>
+      <c r="C225">
+        <v>2</v>
+      </c>
+      <c r="D225" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E225" t="str">
+        <v>address checkbox fix</v>
+      </c>
+      <c r="F225" t="str">
+        <v>407858e401bc2975e70bdf5856f6ab9b140f0960</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>2026-06-18</v>
+      </c>
+      <c r="B226">
+        <v>158484</v>
+      </c>
+      <c r="C226">
+        <v>2</v>
+      </c>
+      <c r="D226" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E226" t="str">
+        <v>add address proof type</v>
+      </c>
+      <c r="F226" t="str">
+        <v>bdb0ea1853713cfe111eda9c06d8564bea6c2b79</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>2026-06-18</v>
+      </c>
+      <c r="B227">
+        <v>158484</v>
+      </c>
+      <c r="C227">
+        <v>4</v>
+      </c>
+      <c r="D227" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E227" t="str">
+        <v>address type mapping</v>
+      </c>
+      <c r="F227" t="str">
+        <v>b405ff6497eaf2fb030c2fed60e43d391b9a8e80</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B228">
+        <v>158484</v>
+      </c>
+      <c r="C228">
+        <v>1</v>
+      </c>
+      <c r="D228" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E228" t="str">
+        <v>single option auto select</v>
+      </c>
+      <c r="F228" t="str">
+        <v>ec9dd5a17c8e072c718bc67e8f05ba8b58e90c53</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B229">
+        <v>158484</v>
+      </c>
+      <c r="C229">
+        <v>1</v>
+      </c>
+      <c r="D229" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E229" t="str">
+        <v>dob check uncheck issue fix</v>
+      </c>
+      <c r="F229" t="str">
+        <v>d168932caf15589c1b9a12a597b27d05a0826231</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B230">
+        <v>158484</v>
+      </c>
+      <c r="C230">
+        <v>1</v>
+      </c>
+      <c r="D230" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E230" t="str">
+        <v>age proof and address proof fix</v>
+      </c>
+      <c r="F230" t="str">
+        <v>08ac7ff4b44fa4830cd3fd240f46d549e398bf83</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B231">
+        <v>158484</v>
+      </c>
+      <c r="C231">
+        <v>1</v>
+      </c>
+      <c r="D231" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E231" t="str">
+        <v>address type details</v>
+      </c>
+      <c r="F231" t="str">
+        <v>632f1d16ccc018a57846aed8211535da54451d74</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B232">
+        <v>158484</v>
+      </c>
+      <c r="C232">
+        <v>1</v>
+      </c>
+      <c r="D232" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E232" t="str">
+        <v>age proof and address proof fix</v>
+      </c>
+      <c r="F232" t="str">
+        <v>b11d955f30d2894156ee9eb98245716aee19704f</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="B233">
+        <v>158484</v>
+      </c>
+      <c r="C233">
+        <v>3</v>
+      </c>
+      <c r="D233" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E233" t="str">
+        <v>address type details</v>
+      </c>
+      <c r="F233" t="str">
+        <v>3a837721569e94449274103a7ec882e69bc4e14d</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>2026-06-26</v>
+      </c>
+      <c r="B234">
+        <v>158484</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+      <c r="D234" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E234" t="str">
+        <v>ulip rider plan code</v>
+      </c>
+      <c r="F234" t="str">
+        <v>84f93450837775e7e63ee19b1ab48edbb7039310</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>2026-06-26</v>
+      </c>
+      <c r="B235">
+        <v>158484</v>
+      </c>
+      <c r="C235">
+        <v>1</v>
+      </c>
+      <c r="D235" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E235" t="str">
+        <v>dont show harcoded error message on annur</v>
+      </c>
+      <c r="F235" t="str">
+        <v>e22e159cd06c15111919b9408eb0d1435b301574</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>2026-06-26</v>
+      </c>
+      <c r="B236">
+        <v>158484</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+      <c r="D236" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E236" t="str">
+        <v>when no rider directly continue</v>
+      </c>
+      <c r="F236" t="str">
+        <v>c250ba72d7414c93b52250f1a5bbc227aae3d2a0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>2026-06-26</v>
+      </c>
+      <c r="B237">
+        <v>158484</v>
+      </c>
+      <c r="C237">
+        <v>1</v>
+      </c>
+      <c r="D237" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E237" t="str">
+        <v>rider plan code for ulip</v>
+      </c>
+      <c r="F237" t="str">
+        <v>50643aac33cb3566db6c57c19a81eec756aa7af0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>2026-06-26</v>
+      </c>
+      <c r="B238">
+        <v>158484</v>
+      </c>
+      <c r="C238">
+        <v>4</v>
+      </c>
+      <c r="D238" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E238" t="str">
+        <v>SPF PDF Product name is Missing</v>
+      </c>
+      <c r="F238" t="str">
+        <v>afd2e3d7ee62e112e81ff865b9269a8ab1bbf3d4</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B239">
+        <v>158484</v>
+      </c>
+      <c r="C239">
+        <v>1</v>
+      </c>
+      <c r="D239" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E239" t="str">
+        <v>open numeric keypad in suatabilyt matrix</v>
+      </c>
+      <c r="F239" t="str">
+        <v>f64f202e90af5d1099e59d83d57f070f934b0d13</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B240">
+        <v>158484</v>
+      </c>
+      <c r="C240">
+        <v>1</v>
+      </c>
+      <c r="D240" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E240" t="str">
+        <v>error on generate BI also condiser gernal error</v>
+      </c>
+      <c r="F240" t="str">
+        <v>48b28334b39accca8f60e61d842d2e08b2e88210</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B241">
+        <v>158484</v>
+      </c>
+      <c r="C241">
+        <v>1</v>
+      </c>
+      <c r="D241" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E241" t="str">
+        <v>promise4growthplus ppt value isssue fix</v>
+      </c>
+      <c r="F241" t="str">
+        <v>8d7da8462d1558b346eafda60080e9e917abdc18</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B242">
+        <v>158484</v>
+      </c>
+      <c r="C242">
+        <v>1</v>
+      </c>
+      <c r="D242" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E242" t="str">
+        <v>height,weight decial logic same as ISNP</v>
+      </c>
+      <c r="F242" t="str">
+        <v>4dfa9dd3d803e4ec3ea56f32a63850c2a4bcbbd7</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="B243">
+        <v>158484</v>
+      </c>
+      <c r="C243">
+        <v>4</v>
+      </c>
+      <c r="D243" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E243" t="str">
+        <v>training api byass temp</v>
+      </c>
+      <c r="F243" t="str">
+        <v>9a8e40da79daed6e65fd0e6ae77f596a4852e663</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="B244">
+        <v>158484</v>
+      </c>
+      <c r="C244">
+        <v>2</v>
+      </c>
+      <c r="D244" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E244" t="str">
+        <v>tpa api integration</v>
+      </c>
+      <c r="F244" t="str">
+        <v>4fdf6e55e458c3a76f5390445d65db36ff5fda3e</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="B245">
+        <v>158484</v>
+      </c>
+      <c r="C245">
+        <v>2</v>
+      </c>
+      <c r="D245" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E245" t="str">
+        <v>tpa api  integration</v>
+      </c>
+      <c r="F245" t="str">
+        <v>74d1761fc719b203749a19a33d9d9b9707b0fbd1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="B246">
+        <v>158484</v>
+      </c>
+      <c r="C246">
+        <v>4</v>
+      </c>
+      <c r="D246" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E246" t="str">
+        <v>DM-23544</v>
+      </c>
+      <c r="F246" t="str">
+        <v>9420abfa690ba5fa1db8814f3c68083639216de2</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="B247">
+        <v>158484</v>
+      </c>
+      <c r="C247">
+        <v>1</v>
+      </c>
+      <c r="D247" t="str">
+        <v>Meeting</v>
+      </c>
+      <c r="E247" t="str">
+        <v>Daily Scrum Call</v>
+      </c>
+      <c r="F247" t="str">
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="B248">
+        <v>158484</v>
+      </c>
+      <c r="C248">
+        <v>8</v>
+      </c>
+      <c r="D248" t="str">
+        <v>Development &amp; Configuration</v>
+      </c>
+      <c r="E248" t="str">
+        <v>fix(insure): enhance staff discount normalization logic</v>
+      </c>
+      <c r="F248" t="str">
+        <v>3c6612d1fe2fd0fcef05bdb56c7836af5b9d6ccf</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F248"/>
   </ignoredErrors>
 </worksheet>
 </file>